--- a/outputs/parcel_locker_analysis.xlsx
+++ b/outputs/parcel_locker_analysis.xlsx
@@ -645,7 +645,7 @@
         <v>0.07946917089143017</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21595</v>
+        <v>14256</v>
       </c>
     </row>
     <row r="5">
